--- a/Acumulado_cierre_ant.xlsx
+++ b/Acumulado_cierre_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-31</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-30</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>92705.44</v>
+        <v>72130.14999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>92705.44</v>
+        <v>72130.14999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6264</v>
+        <v>5132</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83610.77</v>
+        <v>42168.89</v>
       </c>
       <c r="C4" t="n">
-        <v>83610.77</v>
+        <v>42168.89</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5292</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112089.51</v>
+        <v>81206.7</v>
       </c>
       <c r="C5" t="n">
-        <v>112089.51</v>
+        <v>81206.7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>7431</v>
+        <v>5563</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69692.69</v>
+        <v>51319.38</v>
       </c>
       <c r="C6" t="n">
-        <v>69692.69</v>
+        <v>51319.38</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4059</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22598.06</v>
+        <v>19348.98</v>
       </c>
       <c r="C7" t="n">
-        <v>22598.06</v>
+        <v>19348.98</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1969</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33096.66</v>
+        <v>27634.87</v>
       </c>
       <c r="C8" t="n">
-        <v>33096.66</v>
+        <v>27634.87</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1835</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>413793.13</v>
+        <v>293808.97</v>
       </c>
       <c r="C9" t="n">
-        <v>413793.13</v>
+        <v>293808.97</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
